--- a/Katalog_Mikro_Berintegritas.xlsx
+++ b/Katalog_Mikro_Berintegritas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026\SOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026\SOR\mikro-katalog\mikro-katalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC9246E-1A74-4BEA-87ED-88FF90DA63E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6936560-95CE-4382-817A-C28F7AF1F209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="18192" windowHeight="11472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="107">
   <si>
     <t>MIKRO BERINTEGRITAS | KATALOG KAMPANYE</t>
   </si>
@@ -92,9 +92,6 @@
     <t>#MikroBerintegritas #KamusCalo</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1JzJqklEs-ctGzb9PXbBX4bVoFd0yNJX5/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>MB-002</t>
   </si>
   <si>
@@ -114,9 +111,6 @@
     <t>#MikroBerintegritas #Tes3Pertanyaan</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1RSEGZmGjXWBBaK_VIxRdvwI6xLHjr9dY/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>MB-003</t>
   </si>
   <si>
@@ -133,9 +127,6 @@
   </si>
   <si>
     <t>#MikroBerintegritas #StopLapping</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1kwLBbuchiEfN_BX6cIaXjHYH-U6_CpBj/view?usp=sharing</t>
   </si>
   <si>
     <t>Ya</t>
@@ -160,9 +151,6 @@
     <t>#MikroBerintegritas #RedFlagMikro</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1poV4mLj6NZet7Fl1V7uaP6_uAq41PD1S/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>MB-005</t>
   </si>
   <si>
@@ -181,9 +169,6 @@
     <t>#MikroBerintegritas #JurusTolak</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/120ObuD9F0RVHs-Vt6K_FQJ87i5CcbegC/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>MB-006</t>
   </si>
   <si>
@@ -202,9 +187,6 @@
     <t>#MikroBerintegritas #SwipeKiriCalo</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1yqQFLS5ejT1JJJwww1btk5Hov_MlkGzL/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>MB-008</t>
   </si>
   <si>
@@ -220,9 +202,6 @@
   </si>
   <si>
     <t>#MikroBerintegritas</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1BRvA01D6a9FLVOOXlxJ8iIEWjpnyzKRZ/view?usp=drive_link</t>
   </si>
   <si>
     <t>MB-009</t>
@@ -254,9 +233,6 @@
     <t>#TandaTanganBukanJualan #BeraniTolak</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1GYHPAvnwLp6VKoeoBUFuJuVl2Ovj3jac/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>MB-010</t>
   </si>
   <si>
@@ -278,9 +254,6 @@
     <t>#TanpaTopeng #BeraniTolak #AntiFraud</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1sKDOwBcA7WCJvTPeRUvc0C_DJrceLeyq/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>MB-011</t>
   </si>
   <si>
@@ -303,9 +276,6 @@
     <t>Landscape</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1UNJT279A0Iu3JeUIIa7f5oK_FcrW1ZoK/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>MB-012</t>
   </si>
   <si>
@@ -316,9 +286,6 @@
 🎬 CSI: Cabang Selidiki Ini
 Lihat lebih dekat. Temukan yang janggal. Pastikan sebelum lanjut.
 TAHAN. CEK. ESKALASI.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ogdcnVZailFUSDbHD8pQp0cqPMYj4ON9/view?usp=drive_link</t>
   </si>
   <si>
     <t>MB-013</t>
@@ -338,9 +305,6 @@
 Ada yang janggal? Cek ulang.</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1RkT_wru8RqP7IQYhjF2p9aE9jPtUXwMx/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>MB-014</t>
   </si>
   <si>
@@ -352,9 +316,6 @@
 🌩 Jangan tunggu badai.
 Ada yang ganjil? Cek sebelum lanjut.
 🎬 Simak Ramalan Cuaca Fraud hari ini.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/17yP1NbTD5Z65k7adVZ2jI8iT7W7YaJg_/view?usp=drive_link</t>
   </si>
   <si>
     <t>MB-015</t>
@@ -374,9 +335,6 @@
 🎬 RED FLAG — jangan lanjut hanya karena semua bilang aman.</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1ObweXC0yBveyGzPx9jo5IKEx8QFlnsX5/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>PANDUAN PENGELOLAAN KONTEN</t>
   </si>
   <si>
@@ -528,9 +486,6 @@
   <si>
     <t>Satu Yang Nutup Lubang,
 Semua Ketiban</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Kg8bEm36nzXaQLyrtj3sPzBecwRqCeNB/view?usp=drive_link</t>
   </si>
   <si>
     <t>Ketemu Salah Satu ini, Stop Dulu!</t>
@@ -561,57 +516,21 @@
     <t>Portrait</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1KNF6v3y4pBXnZTKNRMCN6UR6iPvZYEXK/view?usp=drive_link</t>
+    <t>Asset</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF18354A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF18354A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -638,27 +557,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF18354A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
@@ -669,6 +567,14 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF18354A"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -717,138 +623,105 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -856,32 +729,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -895,11 +743,12 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -908,6 +757,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="10"/>
         <color rgb="FF18354A"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -928,6 +778,21 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -941,6 +806,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -954,11 +820,27 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -967,6 +849,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -980,6 +863,21 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1000,17 +898,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="KatalogMateri" displayName="KatalogMateri" ref="A5:I22" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="KatalogMateri" displayName="KatalogMateri" ref="A5:I22" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No. " dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ID Konten" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Jenis Media" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Judul" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Caption Lengkap" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Hashtag" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Orientasi" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Link Media" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Sorotan" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Jenis Media" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Judul" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Caption Lengkap" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Hashtag" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Orientasi" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Asset" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Sorotan" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1212,556 +1110,561 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="6" style="10" customWidth="1"/>
-    <col min="2" max="2" width="7.90234375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.90234375" style="10" customWidth="1"/>
-    <col min="4" max="4" width="20.94921875" style="27" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.234375" style="10" customWidth="1"/>
-    <col min="8" max="8" width="26" style="12" customWidth="1"/>
-    <col min="9" max="9" width="13" style="14" customWidth="1"/>
-    <col min="10" max="16384" width="8.76171875" style="14"/>
+    <col min="1" max="1" width="6" style="11" customWidth="1"/>
+    <col min="2" max="2" width="7.90234375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90234375" style="11" customWidth="1"/>
+    <col min="4" max="4" width="20.94921875" style="31" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" style="30" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.234375" style="11" customWidth="1"/>
+    <col min="8" max="8" width="26" style="30" customWidth="1"/>
+    <col min="9" max="9" width="13" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="8.76171875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="10" customFormat="1" ht="25.8">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:9" s="11" customFormat="1">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-    </row>
-    <row r="2" spans="1:9" s="23" customFormat="1" ht="12.9">
-      <c r="A2" s="22" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+    </row>
+    <row r="2" spans="1:9" s="4" customFormat="1">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-    </row>
-    <row r="3" spans="1:9" s="23" customFormat="1" ht="12.9">
-      <c r="A3" s="22" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+    </row>
+    <row r="3" spans="1:9" s="4" customFormat="1">
+      <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="13"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="14"/>
       <c r="F4" s="15"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="13"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="14"/>
       <c r="I4" s="15"/>
     </row>
-    <row r="5" spans="1:9" s="16" customFormat="1">
-      <c r="A5" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="11" t="s">
+    <row r="5" spans="1:9" s="18" customFormat="1">
+      <c r="A5" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="11" t="s">
+      <c r="H5" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="206.4">
-      <c r="A6" s="17">
+      <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="20" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="G6" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="206.4">
+      <c r="A7" s="22">
+        <v>2</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="C7" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="180.6">
+      <c r="A8" s="19">
+        <v>3</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="193.5">
+      <c r="A9" s="22">
+        <v>4</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="24" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="206.4">
-      <c r="A7" s="19">
-        <v>2</v>
-      </c>
-      <c r="B7" s="19" t="s">
+      <c r="G9" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="193.5">
+      <c r="A10" s="19">
+        <v>5</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="180.6">
+      <c r="A11" s="22">
+        <v>6</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="154.80000000000001">
+      <c r="A12" s="22">
+        <v>7</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="167.7">
+      <c r="A13" s="19">
+        <v>8</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="387">
+      <c r="A14" s="22">
+        <v>9</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="232.2">
+      <c r="A15" s="19">
+        <v>10</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="167.7">
+      <c r="A16" s="22">
+        <v>11</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="141.9">
+      <c r="A17" s="19">
+        <v>12</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="21"/>
+      <c r="G17" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="283.8">
+      <c r="A18" s="22">
+        <v>13</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="24"/>
+      <c r="G18" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="154.80000000000001">
+      <c r="A19" s="19">
+        <v>14</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="21"/>
+      <c r="G19" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="232.2">
+      <c r="A20" s="22">
+        <v>15</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="24"/>
+      <c r="G20" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="296.7">
+      <c r="A21" s="26">
+        <v>16</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="I21" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="11">
         <v>17</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="180.6">
-      <c r="A8" s="17">
-        <v>3</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="193.5">
-      <c r="A9" s="19">
-        <v>4</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="193.5">
-      <c r="A10" s="17">
-        <v>5</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="180.6">
-      <c r="A11" s="19">
-        <v>6</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="154.80000000000001">
-      <c r="A12" s="19">
-        <v>7</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H12" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="I12" s="34" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="167.7">
-      <c r="A13" s="17">
-        <v>8</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="387">
-      <c r="A14" s="19">
-        <v>9</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="232.2">
-      <c r="A15" s="17">
-        <v>10</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="167.7">
-      <c r="A16" s="19">
-        <v>11</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="141.9">
-      <c r="A17" s="17">
-        <v>12</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="18"/>
-      <c r="G17" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="283.8">
-      <c r="A18" s="19">
-        <v>13</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I18" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="154.80000000000001">
-      <c r="A19" s="17">
-        <v>14</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" s="18"/>
-      <c r="G19" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="232.2">
-      <c r="A20" s="19">
-        <v>15</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="20"/>
-      <c r="G20" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="331.2">
-      <c r="A21" s="36">
-        <v>16</v>
-      </c>
-      <c r="B21" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="H21" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="I21" s="34" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="D22" s="36"/>
-      <c r="I22" s="34"/>
+      <c r="D22" s="26"/>
+      <c r="I22" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1780,13 +1683,10 @@
       <formula1>"Ya,Tidak"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="H12" r:id="rId1" xr:uid="{F990574E-79AC-45A5-B7B1-346435E2746D}"/>
-    <hyperlink ref="H21" r:id="rId2" xr:uid="{805462C0-1AE2-4D67-898E-C299EC747BEE}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1796,150 +1696,148 @@
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="5"/>
-    <col min="2" max="2" width="15.6640625" style="32"/>
-    <col min="3" max="6" width="15.6640625" style="5"/>
-    <col min="7" max="7" width="30.90234375" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="15.6640625" style="5"/>
+    <col min="1" max="6" width="15.6640625" style="3"/>
+    <col min="7" max="7" width="30.90234375" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="15.6640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.8" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="3" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A11" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="3" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="B11" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="30" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A12" s="6" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="B12" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="31" t="s">
+    </row>
+    <row r="13" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A13" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A5" s="28" t="s">
+      <c r="B13" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="30" t="s">
+    </row>
+    <row r="14" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A14" s="6" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A6" s="29" t="s">
+      <c r="B14" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="31" t="s">
+    </row>
+    <row r="15" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A15" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="B15" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="30" t="s">
+    </row>
+    <row r="16" spans="1:7" ht="23.2" customHeight="1">
+      <c r="A16" s="6" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A8" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="31" t="s">
+      <c r="B16" s="8" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A9" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="30" t="s">
+    <row r="17" spans="1:2" ht="23.2" customHeight="1">
+      <c r="A17" s="5" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A10" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="31" t="s">
+      <c r="B17" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A11" s="28" t="s">
+    <row r="18" spans="1:2" ht="23.2" customHeight="1">
+      <c r="A18" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B18" s="8" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A12" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A13" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A14" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A15" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="23.2" customHeight="1">
-      <c r="A16" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="23.2" customHeight="1">
-      <c r="A17" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="B17" s="30" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="23.2" customHeight="1">
-      <c r="A18" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
